--- a/Egary/Egary.xlsx
+++ b/Egary/Egary.xlsx
@@ -18,13 +18,14 @@
     <sheet sheetId="9" name="الصيانة" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="الإعدادات" state="visible" r:id="rId13"/>
     <sheet sheetId="11" name="سجل التعديلات" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="المستخدمون" state="hidden" r:id="rId15"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8651" uniqueCount="1277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8677" uniqueCount="1294">
   <si>
     <t>إيجاري</t>
   </si>
@@ -3839,7 +3840,7 @@
     <t>آخر كتابة من الموقع</t>
   </si>
   <si>
-    <t>2026-10-09 15:13:46</t>
+    <t>2026-10-10 10:52:13</t>
   </si>
   <si>
     <t>إصدار البنية</t>
@@ -3855,6 +3856,57 @@
   </si>
   <si>
     <t>الكود</t>
+  </si>
+  <si>
+    <t>المستخدم</t>
+  </si>
+  <si>
+    <t>اسم المستخدم</t>
+  </si>
+  <si>
+    <t>كلمة المرور (مشفّرة)</t>
+  </si>
+  <si>
+    <t>مفعّل</t>
+  </si>
+  <si>
+    <t>آخر دخول</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>المدير</t>
+  </si>
+  <si>
+    <t>مدير</t>
+  </si>
+  <si>
+    <t>pbkdf2$120000$b0516fecda139ffd23f828131551415c$52e12d9c59ccf4e48ddba28948deb330f3ffecfcfdf979d4942dc5d6107940c5</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t>موظف المكتب</t>
+  </si>
+  <si>
+    <t>موظف</t>
+  </si>
+  <si>
+    <t>pbkdf2$120000$b58a51da6139631be1f358a8d09f194d$5961a914482fc5a83e7294521c86e7506bb15ecf7ff304dd71ff2d06231df0c6</t>
+  </si>
+  <si>
+    <t>zaer</t>
+  </si>
+  <si>
+    <t>زائر</t>
+  </si>
+  <si>
+    <t>مشاهدة فقط</t>
+  </si>
+  <si>
+    <t>pbkdf2$120000$d4eafbbdc30de3c498a71b5655775c2e$38146298018fbec477acf08007af0b57233f11ac8d0c4e6b822514c9afc4debe</t>
   </si>
 </sst>
 </file>
@@ -11166,16 +11218,17 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>1273</v>
       </c>
@@ -11191,8 +11244,328 @@
       <c r="E1" s="3" t="s">
         <v>565</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>1277</v>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G200"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="90" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E2" t="s">
+        <v>687</v>
+      </c>
+      <c r="F2" s="29">
+        <v>46304</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E3" t="s">
+        <v>687</v>
+      </c>
+      <c r="F3" s="29">
+        <v>46304</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E4" t="s">
+        <v>687</v>
+      </c>
+      <c r="F4" s="29">
+        <v>46304</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="3:3" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="3:3" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <autoFilter ref="A1:G4"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="قيمة غير مسموحة" error="اختر من القائمة: مدير / موظف / مشاهدة فقط" sqref="C10:C200">
+      <formula1>"مدير,موظف,مشاهدة فقط"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="قيمة غير مسموحة" error="اختر من القائمة: مدير / موظف / مشاهدة فقط" sqref="C2:C200">
+      <formula1>"مدير,موظف,مشاهدة فقط"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/Egary/Egary.xlsx
+++ b/Egary/Egary.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8677" uniqueCount="1294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8683" uniqueCount="1299">
   <si>
     <t>إيجاري</t>
   </si>
@@ -1674,7 +1674,7 @@
     <t>01/04/2026</t>
   </si>
   <si>
-    <t>تنتهي قريبًا</t>
+    <t>تنتهي خلال 90 يومًا</t>
   </si>
   <si>
     <t>ending</t>
@@ -3792,6 +3792,21 @@
     <t>أوراق السنوات الموجودة (تُضاف تلقائيًا)</t>
   </si>
   <si>
+    <t>أعلى أرقام الأكواد الصادرة</t>
+  </si>
+  <si>
+    <t>{"P":3,"C":64,"T":86,"INV-2026":509}</t>
+  </si>
+  <si>
+    <t>لا تُعدَّل: تضمن ألا يُعاد استخدام كود محذوف</t>
+  </si>
+  <si>
+    <t>بداية المحاسبة (تلقائي/يدوي)</t>
+  </si>
+  <si>
+    <t>auto = تبدأ من أقدم ورقة سنة · manual = كما ضبطها المدير</t>
+  </si>
+  <si>
     <t>بادئة رقم الفاتورة</t>
   </si>
   <si>
@@ -3840,7 +3855,7 @@
     <t>آخر كتابة من الموقع</t>
   </si>
   <si>
-    <t>2026-10-10 10:52:13</t>
+    <t>2026-10-10 12:59:59</t>
   </si>
   <si>
     <t>إصدار البنية</t>
@@ -3882,7 +3897,7 @@
     <t>مدير</t>
   </si>
   <si>
-    <t>pbkdf2$120000$b0516fecda139ffd23f828131551415c$52e12d9c59ccf4e48ddba28948deb330f3ffecfcfdf979d4942dc5d6107940c5</t>
+    <t>pbkdf2$120000$2a399ba5667533b4f0c3539ea2dda9bc$c81d26d23246b2f03b92df85e7472919122554f3f09d819ef7b916caccf10cd3</t>
   </si>
   <si>
     <t>office</t>
@@ -3894,7 +3909,7 @@
     <t>موظف</t>
   </si>
   <si>
-    <t>pbkdf2$120000$b58a51da6139631be1f358a8d09f194d$5961a914482fc5a83e7294521c86e7506bb15ecf7ff304dd71ff2d06231df0c6</t>
+    <t>pbkdf2$120000$6e87cd2bc9f71469b0d2391c3c7b7019$40355bed31efb5e38d21aa3157e7a6f6821ef8a864666be2d9095e67f9bdba04</t>
   </si>
   <si>
     <t>zaer</t>
@@ -3906,7 +3921,7 @@
     <t>مشاهدة فقط</t>
   </si>
   <si>
-    <t>pbkdf2$120000$d4eafbbdc30de3c498a71b5655775c2e$38146298018fbec477acf08007af0b57233f11ac8d0c4e6b822514c9afc4debe</t>
+    <t>pbkdf2$120000$f7b621f0224fe71430628d668c922100$140188b3ee26c8c0e4f17ec926e93cc6fc18e463410f011aef10fe030acb4480</t>
   </si>
 </sst>
 </file>
@@ -11032,7 +11047,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -11144,18 +11159,18 @@
         <v>1258</v>
       </c>
       <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
         <v>1259</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B11" t="s">
         <v>1261</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>1262</v>
@@ -11165,48 +11180,70 @@
       <c r="A12" t="s">
         <v>1263</v>
       </c>
-      <c r="B12">
-        <v>0.5</v>
+      <c r="B12" t="s">
+        <v>1264</v>
       </c>
       <c r="C12" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1265</v>
-      </c>
-      <c r="B13">
-        <v>50</v>
+        <v>1266</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B14" t="s">
         <v>1268</v>
+      </c>
+      <c r="B14">
+        <v>0.5</v>
       </c>
       <c r="C14" t="s">
         <v>1269</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B15">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="B16" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>1272</v>
-      </c>
-      <c r="B17">
+        <v>1273</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B19">
         <v>2</v>
       </c>
     </row>
@@ -11230,22 +11267,22 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>565</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
     </row>
   </sheetData>
@@ -11270,7 +11307,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>4</v>
@@ -11279,30 +11316,30 @@
         <v>526</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>518</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="B2" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="C2" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="E2" t="s">
         <v>687</v>
@@ -11316,16 +11353,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="B3" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="C3" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="E3" t="s">
         <v>687</v>
@@ -11339,16 +11376,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="B4" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="C4" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="E4" t="s">
         <v>687</v>
